--- a/ProjectProgress/表格/分类进展/交互与AI.xlsx
+++ b/ProjectProgress/表格/分类进展/交互与AI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="Rb8c7a9358add4dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R46da0b4927a04eaa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -175,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H23"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -410,7 +410,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -447,22 +447,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,A5)</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIF(C8:C23,A5)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,D5)</x:f>
+        <x:f>COUNTIF(C8:C23,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,F5)</x:f>
+        <x:f>COUNTIF(C8:C23,F5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -503,27 +503,27 @@
         <x:v>用户备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="92" customHeight="1">
+    <x:row r="8" ht="109" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>CA-002</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>White 30 名实例与三类学生数量接入</x:v>
+        <x:v>scene学生实例数量接入与当前单White保留</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>Student_White_01 至 Student_White_30 已接入校园，各有独立出生巡游锚点；White、Purple、Man 各 30 人，共 90 人。最终 68 次采样均保持 30 名 White。</x:v>
+        <x:v>原30White/30Purple/30Man阶段接入已交付。用户10月4日要求移除非White且只保留一个，现已移除89名并保存，仅Student_White_01；正常PIE与最终scene确认1个角色，108座椅保留。</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>后续增删学生时复核实例数量与独立出生锚点。</x:v>
+        <x:v>当前人数以唯一White为准；历史90人运行数据只属于早期阶段。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>46294</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>White 场景数量、锚点与运行数量检查</x:v>
+        <x:v>用户直接人数纠正与唯一White保存运行检查</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
@@ -532,22 +532,22 @@
         <x:v>CA-003</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>White NavMesh 路径生成与实际绕障</x:v>
+        <x:v>White原生全校园寻路与实际绕障</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>3 条绕过直线受阻绿植的候选路径均有效且非部分路径；1 名 White 定向运行约 10.67 秒，到目标距离 71.07 cm，进入 76 cm 验收范围，腰部静态重叠采样为零。</x:v>
+        <x:v>局部导航已迁入C++，最新扩展为整个可达校园随机选点，支持室内、上下楼和失败重试，修复花坛及建筑导航误通行后12条真实路线通过，32次随机目标完整路径。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>验收范围为 3 次路径查询和 1 次实际遍历；未采集 MoveTo 完成事件。后续改变导航条件时需重验。</x:v>
+        <x:v>实现与具体路线、抽样验收分别见CA-053.09、CA-053.10；不等于每条校园路径通过。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46294</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>定向导航查询与代表角色绕障记录</x:v>
+        <x:v>C++导航迁移与全校园最终保存交付</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -562,16 +562,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>约 44.73 秒、68 次采样中，White 彼此及与其他学生的胶囊穿透次数均为零，没有持续卡住角色。实际控制器使用 DetourCrowdAIController 和 CrowdFollowingComponent。</x:v>
+        <x:v>历史90人环境约44.73秒68采样的胶囊穿透与卡住检查通过。10月3日学生导航迁入C++并运行验证，10月4日按用户要求仅保留1个White，当前不再存在三类90人人群测试条件。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>有限采样不能证明每个瞬间无碰撞；后续人群密度或导航布局修改时继续观察。</x:v>
+        <x:v>原多人避让验收保留为阶段历史；当前单White路线见CA-053.09，不据此承诺多人配置。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46294</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>最终 White 自主巡游、人群分离与卡住检查</x:v>
+        <x:v>原避让基线、C++迁移与最新人数纠正</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
@@ -623,45 +623,309 @@
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-    </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="3" t="str">
+    <x:row r="13" ht="75" customHeight="1">
+      <x:c r="A13" s="7" t="str">
+        <x:v>CA-045</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>Xbox摇杆移动与视角映射</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>第一和第三人称资源中左摇杆映射WASD、右摇杆转视角，并保存帧率补偿。最新用户要求反转右摇杆垂直方向，另见CA-045.03。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>本阶段适用原人物控制器；当前scene观察摄像机映射另见CA-045.05。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>手柄映射最终保存结果</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="7" t="str">
+        <x:v>CA-045.02</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>Xbox Y键门交互映射</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
+        <x:v>Y键映射原E键交互，原键鼠保留；C++迁移后四类门的E/Y、双门联动、距离限制和开关动作32项检查通过。</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>门原生实现保留；当前观察摄像机的交互入口另核对CA-045.05。</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>手柄映射与原生门测试</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="92" customHeight="1">
+      <x:c r="A15" s="7" t="str">
+        <x:v>CA-045.03</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>手柄右摇杆垂直视角反转</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>按用户最新纠正，上推右摇杆向下看、下拉向上看；水平转动、死区和速度保持。第一及第三人称共32项检查通过，保存重载确认，已包含在CPP_InvertY发布包。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>版本交付见CA-046，后续源工程已改为观察摄像机。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>用户纠正、输入回读与发布元数据</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="75" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>CA-052.05</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>White碰撞表面坐下倚靠自动分类</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>用户选择自动触发并保留手动接口。按实际碰撞顶面与脚下地面判断低面坐下、高面倚靠，保留NoRest排除与可达/净空/稳定支撑校验。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>体力模式优先按公共座椅寻座，不把任意模型都当可坐表面。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>用户选择、自适应说明与体力接入</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="92" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>CA-053</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>White C++体力行走消耗</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>体力计算已由C++实现，满值100、低值25；实际地面行走消耗，停留及坐下/起身不扣除。最新全校园行走消耗从1.5调整为每秒0.25并保存。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>以最新单White配置为准，恢复见CA-053.03。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>体力最终参数与全校园交付</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="75" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>CA-053.02</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>White最近可达空座选择与预约</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>比较空座完整导航路径长度选最近可达座椅，按整张木条组合长椅预约；到达后检查支撑和胶囊净空，占用测试通过。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>标记不等于可达，每次寻座重新检查完整路径。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>体力C++寻座与占用测试</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="75" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>CA-053.03</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>White坐稳恢复与满值起身</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>仅坐稳Seated Idle后每秒恢复10，体力回到100才起身并释放预约；不沿用旧8–15秒待机结束规则，完整状态循环通过。</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>续行到原目标独立见CA-053.07。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>qa_stamina_result恢复与满值检查</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="92" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-053.04</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>校园108处公共座椅标记接入</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>scene保存108处CampusPublicSeat标记，组合长椅按整张管理；标记不渲染、不阻挡且不改变导航。单White和全校园版本保留全部引用。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>有标记座椅仍需运行时完整路径和支撑检查。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>最终标记数量与引用检查</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="75" customHeight="1">
+      <x:c r="A21" s="7" t="str">
+        <x:v>CA-053.05</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>White寻座失效与导航失败重试</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>座位失效、停滞或失去控制器释放预约，失败座位临时排除；目标失效测试保持可移动，未找到座椅时重试并保留校园目标。</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>校园目的地连续真实失败达到上限才重新选点。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>体力失效测试与最终运行逻辑</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="75" customHeight="1">
+      <x:c r="A22" s="7" t="str">
+        <x:v>CA-053.07</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>White中途休息后保持原目的地</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>按用户直接纠正，寻最近可达板凳时保留目的地，回满从座椅重规划到原目标，到达后才选新点；绕花坛后抵达原定综合楼五层通过。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>实走12路线见CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>用户续行纠正与修复后完整路线</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="75" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-053.08</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>White经过关闭原生门自动开门</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>行走检测前方约180cm真实阻挡门扇，打开关联CampusDoorActor；支持原生单门、滑门和配对门，教室关闭门实走通过。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>普通静态门模型不会因外观自动打开。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>全校园README与教室实走</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="A25" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B14" s="19" t="str">
+      <x:c r="B25" s="19" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C14" s="19"/>
-      <x:c r="D14" s="19"/>
-      <x:c r="E14" s="19"/>
-      <x:c r="F14" s="19"/>
-      <x:c r="G14" s="19"/>
-      <x:c r="H14" s="19"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
+      <x:c r="C25" s="19"/>
+      <x:c r="D25" s="19"/>
+      <x:c r="E25" s="19"/>
+      <x:c r="F25" s="19"/>
+      <x:c r="G25" s="19"/>
+      <x:c r="H25" s="19"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B14:H14"/>
+    <x:mergeCell ref="B25:H25"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C12">
+  <x:conditionalFormatting sqref="C8:C23">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -673,13 +937,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C12">
+    <x:dataValidation type="list" sqref="C8:C23">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf35680b141ff4c8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R235e782b60ab4493"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/交互与AI.xlsx
+++ b/ProjectProgress/表格/分类进展/交互与AI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R46da0b4927a04eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R27fa943678ee464d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -175,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H24"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -410,7 +410,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -447,22 +447,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,A5)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTIF(C8:C24,A5)</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,D5)</x:f>
+        <x:f>COUNTIF(C8:C24,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,F5)</x:f>
+        <x:f>COUNTIF(C8:C24,F5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -637,13 +637,13 @@
         <x:v>第一和第三人称资源中左摇杆映射WASD、右摇杆转视角，并保存帧率补偿。最新用户要求反转右摇杆垂直方向，另见CA-045.03。</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>本阶段适用原人物控制器；当前scene观察摄像机映射另见CA-045.05。</x:v>
+        <x:v>当前第一人称入口已恢复；最新实体手柄回归范围另见CA-045.05。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>手柄映射最终保存结果</x:v>
+        <x:v>原手柄交付与最新第一人称恢复</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
@@ -661,13 +661,13 @@
         <x:v>Y键映射原E键交互，原键鼠保留；C++迁移后四类门的E/Y、双门联动、距离限制和开关动作32项检查通过。</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>门原生实现保留；当前观察摄像机的交互入口另核对CA-045.05。</x:v>
+        <x:v>E/Y原生实现阶段验收保留；当前同版本范围见CA-045.05。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>手柄映射与原生门测试</x:v>
+        <x:v>原手柄交付与最新第一人称恢复</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
@@ -685,13 +685,13 @@
         <x:v>按用户最新纠正，上推右摇杆向下看、下拉向上看；水平转动、死区和速度保持。第一及第三人称共32项检查通过，保存重载确认，已包含在CPP_InvertY发布包。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>版本交付见CA-046，后续源工程已改为观察摄像机。</x:v>
+        <x:v>垂直反转阶段交付保留，当前第一人称入口及新发布包见CA-018和CA-046.02。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>用户纠正、输入回读与发布元数据</x:v>
+        <x:v>原手柄交付与最新第一人称恢复</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
@@ -887,45 +887,69 @@
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
-    </x:row>
-    <x:row r="25" ht="34" customHeight="1">
-      <x:c r="A25" s="3" t="str">
+    <x:row r="24" ht="75" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-056</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>高三楼一百二十门扇交互接入</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>高三楼120门扇、109交互组、114控制器及252活动部件接入并保存，约2米内E开关；双扇联动，包含卫生间与电梯门。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>通行能力与开关能力分开，窄厕位门洞见CA-056.04。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>高三门部署完成记录</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="1"/>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1"/>
+      <x:c r="H25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="34" customHeight="1">
+      <x:c r="A26" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B25" s="19" t="str">
+      <x:c r="B26" s="19" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C25" s="19"/>
-      <x:c r="D25" s="19"/>
-      <x:c r="E25" s="19"/>
-      <x:c r="F25" s="19"/>
-      <x:c r="G25" s="19"/>
-      <x:c r="H25" s="19"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
+      <x:c r="C26" s="19"/>
+      <x:c r="D26" s="19"/>
+      <x:c r="E26" s="19"/>
+      <x:c r="F26" s="19"/>
+      <x:c r="G26" s="19"/>
+      <x:c r="H26" s="19"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1"/>
+      <x:c r="D27" s="1"/>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="1"/>
+      <x:c r="G27" s="1"/>
+      <x:c r="H27" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B25:H25"/>
+    <x:mergeCell ref="B26:H26"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C23">
+  <x:conditionalFormatting sqref="C8:C24">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -937,13 +961,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C23">
+    <x:dataValidation type="list" sqref="C8:C24">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R235e782b60ab4493"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752c0eee4a284ffc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/交互与AI.xlsx
+++ b/ProjectProgress/表格/分类进展/交互与AI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R27fa943678ee464d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R7cca0102e50349d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -410,7 +410,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -508,22 +508,22 @@
         <x:v>CA-002</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>scene学生实例数量接入与当前单White保留</x:v>
+        <x:v>scene当前150名White学生数量接入</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>原30White/30Purple/30Man阶段接入已交付。用户10月4日要求移除非White且只保留一个，现已移除89名并保存，仅Student_White_01；正常PIE与最终scene确认1个角色，108座椅保留。</x:v>
+        <x:v>10月6日用户要求总计150名White，替代10月4日单人配置。新增149名，位置通过完整路径和胶囊检查；scene已保存，运行全程150人，基准测试后位置与直立姿态保持，108座椅引用有效。</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>当前人数以唯一White为准；历史90人运行数据只属于早期阶段。</x:v>
+        <x:v>当前学生人数以150名White为准；旧90人及单White仅保留阶段历史，玩家角色不计入学生。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>用户直接人数纠正与唯一White保存运行检查</x:v>
+        <x:v>最新150人直接需求、关卡保存与最终验证</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
@@ -556,19 +556,19 @@
         <x:v>CA-003.02</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>White DetourCrowd 人群避让与持续卡住检查</x:v>
+        <x:v>White历史90人避让与持续卡住阶段验收</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>历史90人环境约44.73秒68采样的胶囊穿透与卡住检查通过。10月3日学生导航迁入C++并运行验证，10月4日按用户要求仅保留1个White，当前不再存在三类90人人群测试条件。</x:v>
+        <x:v>历史90人约44.73秒68采样的胶囊穿透与卡住检查通过；10月4日单人阶段后，10月6日最新配置已改150名White。旧三类90人结果保留为阶段历史。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>原多人避让验收保留为阶段历史；当前单White路线见CA-053.09，不据此承诺多人配置。</x:v>
+        <x:v>最新150人移动与控制器验证见CA-072.04；该新样本不等于逐对穿透或所有长期卡住验收。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>原避让基线、C++迁移与最新人数纠正</x:v>
@@ -733,10 +733,10 @@
         <x:v>体力计算已由C++实现，满值100、低值25；实际地面行走消耗，停留及坐下/起身不扣除。最新全校园行走消耗从1.5调整为每秒0.25并保存。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>以最新单White配置为准，恢复见CA-053.03。</x:v>
+        <x:v>当前150人均观察到行走扣体力，见CA-072.04；恢复抽查与座位限制见CA-072.05。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>体力最终参数与全校园交付</x:v>
@@ -802,13 +802,13 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>scene保存108处CampusPublicSeat标记，组合长椅按整张管理；标记不渲染、不阻挡且不改变导航。单White和全校园版本保留全部引用。</x:v>
+        <x:v>scene保存108处CampusPublicSeat标记，组合长椅按整张管理；标记不渲染、不阻挡且不改变导航。最新150人交付后108处座椅与全部引用仍有效。</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
         <x:v>有标记座椅仍需运行时完整路径和支撑检查。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>最终标记数量与引用检查</x:v>
@@ -967,7 +967,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752c0eee4a284ffc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dc7ec8a157b443a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/交互与AI.xlsx
+++ b/ProjectProgress/表格/分类进展/交互与AI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R7cca0102e50349d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R6646b157e75a46b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -80,7 +80,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -175,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H25"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -410,7 +416,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -422,7 +428,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>门交互部署、学生接入、寻路及人群避让。</x:v>
+        <x:v>门及灯光交互部署、学生接入、寻路及人群避让。</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
@@ -447,22 +453,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,A5)</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTIF(C8:C25,A5)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,D5)</x:f>
+        <x:f>COUNTIF(C8:C25,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,F5)</x:f>
+        <x:f>COUNTIF(C8:C25,F5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -519,8 +525,8 @@
       <x:c r="E8" s="7" t="str">
         <x:v>当前学生人数以150名White为准；旧90人及单White仅保留阶段历史，玩家角色不计入学生。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F8" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
         <x:v>最新150人直接需求、关卡保存与最终验证</x:v>
@@ -543,8 +549,8 @@
       <x:c r="E9" s="7" t="str">
         <x:v>实现与具体路线、抽样验收分别见CA-053.09、CA-053.10；不等于每条校园路径通过。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F9" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>C++导航迁移与全校园最终保存交付</x:v>
@@ -567,8 +573,8 @@
       <x:c r="E10" s="7" t="str">
         <x:v>最新150人移动与控制器验证见CA-072.04；该新样本不等于逐对穿透或所有长期卡住验收。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F10" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>原避让基线、C++迁移与最新人数纠正</x:v>
@@ -591,8 +597,8 @@
       <x:c r="E11" s="7" t="str">
         <x:v>在后续主地图改动中复核门数量、附属零件和正常闭合状态。</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46292</x:v>
+      <x:c r="F11" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
         <x:v>教室门交互说明：96 门部署与验证</x:v>
@@ -615,8 +621,8 @@
       <x:c r="E12" s="7" t="str">
         <x:v>门框、门扇或门洞调整后复核双侧响应及通行。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
-        <x:v>46292</x:v>
+      <x:c r="F12" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>教师楼双门最新聊天与完成记录</x:v>
@@ -639,8 +645,8 @@
       <x:c r="E13" s="7" t="str">
         <x:v>当前第一人称入口已恢复；最新实体手柄回归范围另见CA-045.05。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F13" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>原手柄交付与最新第一人称恢复</x:v>
@@ -663,8 +669,8 @@
       <x:c r="E14" s="7" t="str">
         <x:v>E/Y原生实现阶段验收保留；当前同版本范围见CA-045.05。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F14" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>原手柄交付与最新第一人称恢复</x:v>
@@ -687,8 +693,8 @@
       <x:c r="E15" s="7" t="str">
         <x:v>垂直反转阶段交付保留，当前第一人称入口及新发布包见CA-018和CA-046.02。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F15" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
         <x:v>原手柄交付与最新第一人称恢复</x:v>
@@ -711,8 +717,8 @@
       <x:c r="E16" s="7" t="str">
         <x:v>体力模式优先按公共座椅寻座，不把任意模型都当可坐表面。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F16" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>用户选择、自适应说明与体力接入</x:v>
@@ -735,8 +741,8 @@
       <x:c r="E17" s="7" t="str">
         <x:v>当前150人均观察到行走扣体力，见CA-072.04；恢复抽查与座位限制见CA-072.05。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F17" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>体力最终参数与全校园交付</x:v>
@@ -759,8 +765,8 @@
       <x:c r="E18" s="7" t="str">
         <x:v>标记不等于可达，每次寻座重新检查完整路径。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
         <x:v>体力C++寻座与占用测试</x:v>
@@ -783,8 +789,8 @@
       <x:c r="E19" s="7" t="str">
         <x:v>续行到原目标独立见CA-053.07。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F19" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
         <x:v>qa_stamina_result恢复与满值检查</x:v>
@@ -807,8 +813,8 @@
       <x:c r="E20" s="7" t="str">
         <x:v>有标记座椅仍需运行时完整路径和支撑检查。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F20" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>最终标记数量与引用检查</x:v>
@@ -831,8 +837,8 @@
       <x:c r="E21" s="7" t="str">
         <x:v>校园目的地连续真实失败达到上限才重新选点。</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F21" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>体力失效测试与最终运行逻辑</x:v>
@@ -855,8 +861,8 @@
       <x:c r="E22" s="7" t="str">
         <x:v>实走12路线见CA-053.09。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F22" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
         <x:v>用户续行纠正与修复后完整路线</x:v>
@@ -879,8 +885,8 @@
       <x:c r="E23" s="7" t="str">
         <x:v>普通静态门模型不会因外观自动打开。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F23" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
         <x:v>全校园README与教室实走</x:v>
@@ -903,53 +909,77 @@
       <x:c r="E24" s="7" t="str">
         <x:v>通行能力与开关能力分开，窄厕位门洞见CA-056.04。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
         <x:v>高三门部署完成记录</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="1"/>
-      <x:c r="B25" s="1"/>
-      <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-      <x:c r="H25" s="1"/>
-    </x:row>
-    <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="3" t="str">
+    <x:row r="25" ht="75" customHeight="1">
+      <x:c r="A25" s="7" t="str">
+        <x:v>CA-074</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>五栋楼墙壁灯光开关部署</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>教学楼A/B、综合楼、食堂、高三楼已保存254个墙壁开关，覆盖161个照明回路和728个灯具对象。教室独立控制，走廊和楼梯多点联动。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>当前范围为指定五栋楼；室外独立庭院不在该部署范围。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>最终交付与complete=true</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B26" s="19" t="str">
+      <x:c r="B27" s="19" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C26" s="19"/>
-      <x:c r="D26" s="19"/>
-      <x:c r="E26" s="19"/>
-      <x:c r="F26" s="19"/>
-      <x:c r="G26" s="19"/>
-      <x:c r="H26" s="19"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="1"/>
-      <x:c r="B27" s="1"/>
-      <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-      <x:c r="H27" s="1"/>
+      <x:c r="C27" s="19"/>
+      <x:c r="D27" s="19"/>
+      <x:c r="E27" s="19"/>
+      <x:c r="F27" s="19"/>
+      <x:c r="G27" s="19"/>
+      <x:c r="H27" s="19"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B26:H26"/>
+    <x:mergeCell ref="B27:H27"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C24">
+  <x:conditionalFormatting sqref="C8:C25">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -961,13 +991,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C24">
+    <x:dataValidation type="list" sqref="C8:C25">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dc7ec8a157b443a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R738be73d889c45ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/交互与AI.xlsx
+++ b/ProjectProgress/表格/分类进展/交互与AI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R6646b157e75a46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互与AI" sheetId="1" r:id="R88f0f636d3e8477d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress5" displayName="CategoryProgress5" ref="A7:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H27"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -416,7 +416,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -453,22 +453,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,A5)</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTIF(C8:C27,A5)</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,D5)</x:f>
+        <x:f>COUNTIF(C8:C27,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,F5)</x:f>
+        <x:f>COUNTIF(C8:C27,F5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -917,7 +917,7 @@
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
-    <x:row r="25" ht="75" customHeight="1">
+    <x:row r="25" ht="109" customHeight="1">
       <x:c r="A25" s="7" t="str">
         <x:v>CA-074</x:v>
       </x:c>
@@ -928,42 +928,66 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>教学楼A/B、综合楼、食堂、高三楼已保存254个墙壁开关，覆盖161个照明回路和728个灯具对象。教室独立控制，走廊和楼梯多点联动。</x:v>
+        <x:v>10月9日用户反馈看到提示但灯光无变化后，五栋楼254开关/161回路补齐真实照明并保存重开，初始全部关闭。10月10日A/B教室合并进一步调整房号和回路，见CA-079.04；254/161为修复阶段完整覆盖数。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>当前范围为指定五栋楼；室外独立庭院不在该部署范围。</x:v>
+        <x:v>部署已交付；教室合并后的回路与室内灯光按CA-079、CA-080阶段证据跟踪，不把旧数量视作最新全场重计数。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>最终交付与complete=true</x:v>
+        <x:v>用户灯光无变化纠正、修复completion和重开验证</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-    </x:row>
-    <x:row r="27" ht="34" customHeight="1">
-      <x:c r="A27" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B27" s="19" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C27" s="19"/>
-      <x:c r="D27" s="19"/>
-      <x:c r="E27" s="19"/>
-      <x:c r="F27" s="19"/>
-      <x:c r="G27" s="19"/>
-      <x:c r="H27" s="19"/>
+    <x:row r="26" ht="75" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-077.02</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>PS5摇杆跳跃与三角键交互映射</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>复用左摇杆移动、右摇杆视角、×跳跃、△对应E/Y门灯交互；配置回读与通用映射检查通过，键鼠与Xbox支持保留。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>实现映射已交付；hardware_input_tested=false，不能当作真实PS5按键逐项通过。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>最新聊天最终操作表与映射检查</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="75" customHeight="1">
+      <x:c r="A27" s="7" t="str">
+        <x:v>CA-079.04</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>合并教室前后开关联动同一回路</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>两侧原灯具接入同一合并教室回路，前后开关共同控制整间教室，24间运行检查通过，默认关闭规则沿用CA-074.02。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>新室内吊灯材质和48昼夜案例见CA-080.09；未重新清点全五栋楼面板总数。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>runtime_collision_and_lights_verified与最终聊天</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1"/>
@@ -975,11 +999,35 @@
       <x:c r="G28" s="1"/>
       <x:c r="H28" s="1"/>
     </x:row>
+    <x:row r="29" ht="34" customHeight="1">
+      <x:c r="A29" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B29" s="19" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C29" s="19"/>
+      <x:c r="D29" s="19"/>
+      <x:c r="E29" s="19"/>
+      <x:c r="F29" s="19"/>
+      <x:c r="G29" s="19"/>
+      <x:c r="H29" s="19"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B27:H27"/>
+    <x:mergeCell ref="B29:H29"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C25">
+  <x:conditionalFormatting sqref="C8:C27">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -991,13 +1039,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C25">
+    <x:dataValidation type="list" sqref="C8:C27">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R738be73d889c45ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d14f39c7fe42b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>